--- a/riobamba-censo-data/shp/plataforma_l.xlsx
+++ b/riobamba-censo-data/shp/plataforma_l.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -498,11 +498,12 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,25 +534,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>edad0_14</t>
+          <t>edad0_4</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>edad15_29</t>
+          <t>edad5_11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>edad30_44</t>
+          <t>edad12_17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>edad45_64</t>
+          <t>edad18_29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>edad30_64</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>edad65mas</t>
         </is>
@@ -578,18 +584,21 @@
         <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
+        <v>47</v>
+      </c>
+      <c r="K2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -614,18 +623,21 @@
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="H3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
       <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -650,18 +662,21 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -686,18 +701,21 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -722,18 +740,21 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -758,18 +779,21 @@
         <v>9</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -794,18 +818,21 @@
         <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
+        <v>42</v>
+      </c>
+      <c r="K8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -830,18 +857,21 @@
         <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>8</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -866,18 +896,21 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -902,18 +935,21 @@
         <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
       </c>
       <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -938,18 +974,21 @@
         <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
         <v>16</v>
       </c>
-      <c r="I12" t="n">
-        <v>19</v>
-      </c>
       <c r="J12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -974,18 +1013,21 @@
         <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J13" t="n">
+        <v>35</v>
+      </c>
+      <c r="K13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1010,18 +1052,21 @@
         <v>26</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
+        <v>27</v>
+      </c>
+      <c r="K14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1046,18 +1091,21 @@
         <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I15" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
+        <v>79</v>
+      </c>
+      <c r="K15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1082,18 +1130,21 @@
         <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1118,10 +1169,10 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1130,6 +1181,9 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1154,18 +1208,21 @@
         <v>125</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H18" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="I18" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="J18" t="n">
+        <v>118</v>
+      </c>
+      <c r="K18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1190,18 +1247,21 @@
         <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
+        <v>53</v>
+      </c>
+      <c r="K19" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1226,18 +1286,21 @@
         <v>136</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="H20" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="J20" t="n">
+        <v>105</v>
+      </c>
+      <c r="K20" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1262,18 +1325,21 @@
         <v>131</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="H21" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="I21" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="J21" t="n">
+        <v>102</v>
+      </c>
+      <c r="K21" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1298,18 +1364,21 @@
         <v>78</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="J22" t="n">
+        <v>70</v>
+      </c>
+      <c r="K22" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1334,18 +1403,21 @@
         <v>51</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="J23" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1370,18 +1442,21 @@
         <v>42</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1406,18 +1481,21 @@
         <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H25" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J25" t="n">
+        <v>74</v>
+      </c>
+      <c r="K25" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1442,18 +1520,21 @@
         <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1478,18 +1559,21 @@
         <v>22</v>
       </c>
       <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
         <v>9</v>
       </c>
-      <c r="G27" t="n">
-        <v>8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>12</v>
-      </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1514,18 +1598,21 @@
         <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H28" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J28" t="n">
+        <v>45</v>
+      </c>
+      <c r="K28" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1550,18 +1637,21 @@
         <v>47</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>21</v>
       </c>
       <c r="J29" t="n">
+        <v>40</v>
+      </c>
+      <c r="K29" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1586,18 +1676,21 @@
         <v>19</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1628,12 +1721,15 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1658,18 +1754,21 @@
         <v>59</v>
       </c>
       <c r="F32" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
+        <v>45</v>
+      </c>
+      <c r="K32" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1694,18 +1793,21 @@
         <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1733,20 +1835,23 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>